--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoni\jmocha\DevelopmentDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ezEKP\work___24(디자인진흥원)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -239,10 +239,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사용자 이메일 주소 (email_id@email_domain)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 방법이 제공되어야 합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -259,24 +255,28 @@
   </si>
   <si>
     <t>* 부서아이디(dept_id, parent_dept_id)를 구성하는 문자로는 영소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
+  </si>
+  <si>
+    <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 시스템 내에서 사용할 이메일 주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -285,7 +285,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -293,7 +293,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -739,17 +739,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="0.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.7109375" customWidth="1"/>
+    <col min="1" max="1" width="0.75" customWidth="1"/>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
@@ -758,7 +758,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -769,7 +769,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -780,7 +780,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -789,7 +789,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -806,7 +806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
@@ -823,7 +823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
@@ -838,7 +838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -851,7 +851,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="30">
+    <row r="12" spans="2:6" ht="33" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>57</v>
       </c>
@@ -866,7 +866,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
@@ -879,25 +879,25 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="7"/>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="7"/>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>59</v>
       </c>
@@ -919,17 +919,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:F29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.140625" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="84.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.125" customWidth="1"/>
+    <col min="2" max="2" width="24.125" customWidth="1"/>
+    <col min="3" max="3" width="13.875" customWidth="1"/>
+    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
@@ -938,7 +938,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -949,7 +949,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -960,7 +960,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -969,7 +969,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>63</v>
       </c>
@@ -1071,10 +1071,10 @@
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>60</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
@@ -1217,17 +1217,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>59</v>
       </c>
@@ -1248,17 +1248,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:F14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.5703125" customWidth="1"/>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>52</v>
       </c>
@@ -1267,7 +1267,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1278,7 +1278,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1289,7 +1289,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1329,10 +1329,10 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1346,10 +1346,10 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>59</v>
       </c>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ezEKP\work___24(디자인진흥원)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="77">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -259,24 +259,27 @@
   <si>
     <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 시스템 내에서 사용할 이메일 주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 사용자 아이디와 부서 아이디는 서로 중복되지 않는 유일한 값이어야 합니다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -285,7 +288,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -293,7 +296,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -385,7 +388,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -432,6 +435,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,17 +745,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:F18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="0.75" customWidth="1"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.75" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6">
       <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
@@ -758,7 +764,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -769,7 +775,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -780,7 +786,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -789,7 +795,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -806,7 +812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
@@ -823,7 +829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6">
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
@@ -838,7 +844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -851,7 +857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="30">
       <c r="B12" s="6" t="s">
         <v>57</v>
       </c>
@@ -866,7 +872,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
@@ -879,25 +885,25 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6">
       <c r="B15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="7"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6">
       <c r="B16" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3">
       <c r="B17" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C17" s="7"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3">
       <c r="B18" s="7" t="s">
         <v>59</v>
       </c>
@@ -918,18 +924,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B4:F30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.125" customWidth="1"/>
-    <col min="2" max="2" width="24.125" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="84.375" customWidth="1"/>
+    <col min="1" max="1" width="1.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6">
       <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
@@ -938,7 +944,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -949,7 +955,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -960,7 +966,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -969,7 +975,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -986,7 +992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6">
       <c r="B11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1046,7 +1052,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6">
       <c r="B14" s="5" t="s">
         <v>63</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6">
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1087,7 +1093,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6">
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6">
       <c r="B17" s="1" t="s">
         <v>60</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6">
       <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6">
       <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
@@ -1139,7 +1145,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6">
       <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6">
       <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
@@ -1165,7 +1171,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6">
       <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
@@ -1191,7 +1197,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
@@ -1217,19 +1223,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6">
       <c r="B28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6">
       <c r="B29" s="7" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="16" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1248,17 +1259,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:F14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.625" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6">
       <c r="B4" s="10" t="s">
         <v>52</v>
       </c>
@@ -1267,7 +1278,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1278,7 +1289,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1289,7 +1300,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1309,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1315,7 +1326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1332,7 +1343,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,7 +1360,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1362,7 +1373,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6">
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1375,7 +1386,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6">
       <c r="B14" s="7" t="s">
         <v>59</v>
       </c>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>로그인 암호</t>
-  </si>
-  <si>
     <t>겸직 Table</t>
   </si>
   <si>
@@ -239,10 +236,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 방법이 제공되어야 합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -257,11 +250,16 @@
     <t>* 부서아이디(dept_id, parent_dept_id)를 구성하는 문자로는 영소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
   </si>
   <si>
-    <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 시스템 내에서 사용할 이메일 주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>* 사용자 아이디와 부서 아이디는 서로 중복되지 않는 유일한 값이어야 합니다.</t>
+  </si>
+  <si>
+    <t>초기 로그인 암호 (처음 사용자 생성 시에만 사용됨)</t>
+  </si>
+  <si>
+    <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 조직도 내에서 사용할 이메일 주소</t>
+  </si>
+  <si>
+    <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 별도의 방법(HTTP 다운로드 같은)이 제공되어야 합니다.</t>
   </si>
 </sst>
 </file>
@@ -419,6 +417,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,9 +436,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -756,44 +754,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
+      <c r="B7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -854,12 +852,12 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30">
       <c r="B12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>20</v>
@@ -869,7 +867,7 @@
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:6">
@@ -887,25 +885,25 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="7"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="7"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="7"/>
     </row>
@@ -932,48 +930,48 @@
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="84.42578125" customWidth="1"/>
+    <col min="6" max="6" width="86" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
+      <c r="B7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -994,7 +992,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1006,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1026,7 +1024,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
@@ -1034,7 +1032,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -1067,7 +1065,7 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>11</v>
@@ -1108,7 +1106,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>33</v>
@@ -1116,7 +1114,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1220,27 +1218,27 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="16" t="s">
-        <v>76</v>
+      <c r="B30" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1270,44 +1268,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
+      <c r="B4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
+      <c r="C5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -1328,7 +1326,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1340,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1357,7 +1355,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1383,12 +1381,12 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="74">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -191,12 +191,6 @@
     <t>정렬순서(겸직 부서 내에서의 사용자의 표시 순서)</t>
   </si>
   <si>
-    <t>dept_level</t>
-  </si>
-  <si>
-    <t>* dept_level 컬럼은 상위부서를 먼저 처리하고 하위부서를 처리하기 위해 전체 테이블을 정렬하는 데에 사용됩니다.</t>
-  </si>
-  <si>
     <t>* 문자열 인코딩은 UTF-8을 사용합니다.</t>
   </si>
   <si>
@@ -213,21 +207,12 @@
   </si>
   <si>
     <t>사번</t>
-  </si>
-  <si>
-    <t>조직도 트리에서의 부서가 위치한 Level
-예) 최상위 부서의 경우 1, 그 다음 하위부서의 경우 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>상위부서 ID (최상위 부서의 경우 NULL)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* 최상위 부서를 나타내는 레코드는 parent_dept_id가 NULL 입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>user_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -260,6 +245,9 @@
   </si>
   <si>
     <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 별도의 방법(HTTP 다운로드 같은)이 제공되어야 합니다.</t>
+  </si>
+  <si>
+    <t>* 최상위 부서를 나타내는 레코드는 parent_dept_id가 NULL 혹은 empty string입니다.</t>
   </si>
 </sst>
 </file>
@@ -300,7 +288,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,12 +298,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -405,14 +387,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -742,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F18"/>
+  <dimension ref="B4:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
@@ -754,44 +730,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -852,60 +828,39 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="30">
-      <c r="B12" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="7"/>
+      <c r="C16" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -934,44 +889,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -992,7 +947,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1004,7 +959,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1024,7 +979,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
@@ -1032,7 +987,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -1065,17 +1020,17 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9" t="s">
-        <v>75</v>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1106,7 +1061,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>33</v>
@@ -1114,7 +1069,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1218,27 +1173,27 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="7" t="s">
-        <v>58</v>
+      <c r="B29" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="10" t="s">
-        <v>73</v>
+      <c r="B30" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1268,44 +1223,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -1326,7 +1281,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1338,7 +1293,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1355,7 +1310,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1385,8 +1340,8 @@
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="7" t="s">
-        <v>58</v>
+      <c r="B14" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="77">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>* 최상위 부서를 나타내는 레코드는 parent_dept_id가 NULL 혹은 empty string입니다.</t>
+  </si>
+  <si>
+    <t>* 이 테이블에서 삭제된 부서는 그룹웨어에서 폐지부서로 처리됩니다.</t>
+  </si>
+  <si>
+    <t>* 이 테이블에서 삭제된 사용자는 그룹웨어에서 퇴직자로 처리됩니다.</t>
+  </si>
+  <si>
+    <t>* 이 테이블에서 삭제된 겸직은 그룹웨어에서도 삭제 처리됩니다.</t>
   </si>
 </sst>
 </file>
@@ -718,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F16"/>
+  <dimension ref="B4:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
@@ -861,6 +870,11 @@
         <v>56</v>
       </c>
       <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="8" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -877,7 +891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F30"/>
+  <dimension ref="B4:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -1194,6 +1208,11 @@
     <row r="30" spans="2:6">
       <c r="B30" s="8" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F14"/>
+  <dimension ref="B4:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -1344,6 +1363,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:F4"/>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="2"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -229,12 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>* 사용자 아이디(user_id, email_id)를 구성하는 문자로는 영소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
-  </si>
-  <si>
-    <t>* 부서아이디(dept_id, parent_dept_id)를 구성하는 문자로는 영소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
-  </si>
-  <si>
     <t>* 사용자 아이디와 부서 아이디는 서로 중복되지 않는 유일한 값이어야 합니다.</t>
   </si>
   <si>
@@ -250,13 +244,40 @@
     <t>* 최상위 부서를 나타내는 레코드는 parent_dept_id가 NULL 혹은 empty string입니다.</t>
   </si>
   <si>
-    <t>* 이 테이블에서 삭제된 부서는 그룹웨어에서 폐지부서로 처리됩니다.</t>
-  </si>
-  <si>
-    <t>* 이 테이블에서 삭제된 사용자는 그룹웨어에서 퇴직자로 처리됩니다.</t>
-  </si>
-  <si>
     <t>* 이 테이블에서 삭제된 겸직은 그룹웨어에서도 삭제 처리됩니다.</t>
+  </si>
+  <si>
+    <t>profile_image_url</t>
+  </si>
+  <si>
+    <t>사용자 사진이 HTTP 다운로드로 제공될 경우 해당 URL</t>
+  </si>
+  <si>
+    <t>* 사용자 아이디(user_id, email_id)를 구성하는 문자로는 영문소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
+  </si>
+  <si>
+    <t>* 부서아이디(dept_id, parent_dept_id)를 구성하는 문자로는 영문소문자, 숫자, dash(-), underscore(_), period(.) 가 가능합니다.</t>
+  </si>
+  <si>
+    <t>* 재직자의 use_yn 컬럼값을 n으로 설정하면 인사연동 시 그룹웨어에서 퇴직자로 처리됩니다.</t>
+  </si>
+  <si>
+    <t>* 퇴직자는 퇴직자관리 메뉴로 이동하며 관리자가 수동으로 삭제할 때만 그룹웨어에서 삭제됩니다.</t>
+  </si>
+  <si>
+    <t>use_yn</t>
+  </si>
+  <si>
+    <t>varchar(1)</t>
+  </si>
+  <si>
+    <t>퇴직구분(y: 재직, n:퇴직)</t>
+  </si>
+  <si>
+    <t>사용구분(y: 유효부서, n:폐지부서)</t>
+  </si>
+  <si>
+    <t>* 유효부서의 use_yn 컬럼값을 n으로 설정하면 인사연동 시 그룹웨어에서 폐지부서로 처리됩니다.</t>
   </si>
 </sst>
 </file>
@@ -727,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F17"/>
+  <dimension ref="B4:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
@@ -853,27 +874,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="6"/>
+    <row r="13" spans="2:6">
+      <c r="B13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="6" t="s">
-        <v>68</v>
+      <c r="B15" t="s">
+        <v>71</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="8" t="s">
-        <v>74</v>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -891,7 +927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F31"/>
+  <dimension ref="B4:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -1044,7 +1080,7 @@
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1054,7 +1090,9 @@
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
         <v>29</v>
@@ -1166,53 +1204,86 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
-      <c r="B27" t="s">
+    <row r="31" spans="2:6">
+      <c r="B31" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="8" t="s">
-        <v>75</v>
+    <row r="33" spans="2:2">
+      <c r="B33" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1365,7 +1436,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -235,9 +235,6 @@
     <t>초기 로그인 암호 (처음 사용자 생성 시에만 사용됨)</t>
   </si>
   <si>
-    <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 조직도 내에서 사용할 이메일 주소</t>
-  </si>
-  <si>
     <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 별도의 방법(HTTP 다운로드 같은)이 제공되어야 합니다.</t>
   </si>
   <si>
@@ -278,6 +275,10 @@
   </si>
   <si>
     <t>* 유효부서의 use_yn 컬럼값을 n으로 설정하면 인사연동 시 그룹웨어에서 폐지부서로 처리됩니다.</t>
+  </si>
+  <si>
+    <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 조직도 내에서 사용할 이메일 주소
+주의) user@naver.com과 같은 외부주소가 아님</t>
   </si>
 </sst>
 </file>
@@ -398,7 +399,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -443,6 +444,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -876,28 +880,28 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="6"/>
     </row>
@@ -909,7 +913,7 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" ht="45">
       <c r="B14" s="5" t="s">
         <v>60</v>
       </c>
@@ -1079,8 +1083,8 @@
         <v>12</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
-        <v>69</v>
+      <c r="F14" s="15" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1204,7 +1208,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1212,7 +1216,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -1243,27 +1247,27 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -1278,12 +1282,12 @@
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +1440,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>varchar(20)</t>
-  </si>
-  <si>
-    <t>생일</t>
   </si>
   <si>
     <t>password</t>
@@ -279,6 +276,15 @@
   <si>
     <t>사용자 이메일 주소 (email_id@email_domain) - 사용자가 조직도 내에서 사용할 이메일 주소
 주의) user@naver.com과 같은 외부주소가 아님</t>
+  </si>
+  <si>
+    <t>생일 (yyyy-mm-dd)</t>
+  </si>
+  <si>
+    <t>birthtype</t>
+  </si>
+  <si>
+    <t>양/음력 구분 (Y:양력, N:음력)</t>
   </si>
 </sst>
 </file>
@@ -427,6 +433,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -444,9 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,44 +770,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="B7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -862,7 +868,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -880,40 +886,40 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="6"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F34"/>
+  <dimension ref="B4:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -943,44 +949,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="B7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -1001,7 +1007,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1013,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1033,7 +1039,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
@@ -1041,7 +1047,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -1074,7 +1080,7 @@
     </row>
     <row r="14" spans="2:6" ht="45">
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>11</v>
@@ -1083,8 +1089,8 @@
         <v>12</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="15" t="s">
-        <v>83</v>
+      <c r="F14" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1117,7 +1123,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>33</v>
@@ -1125,7 +1131,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1208,7 +1214,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1216,7 +1222,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -1229,65 +1235,78 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="6" t="s">
-        <v>56</v>
+      <c r="B31" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="8" t="s">
-        <v>67</v>
+      <c r="B32" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1317,44 +1336,44 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:6">
-      <c r="B4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="C5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="3" t="s">
@@ -1375,7 +1394,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1387,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1404,7 +1423,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1430,17 +1449,17 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tech/인사연동_테이블정의서.xlsx
+++ b/docs/tech/인사연동_테이블정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="87">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>양/음력 구분 (Y:양력, N:음력)</t>
+  </si>
+  <si>
+    <t>* 마지막 인사연동후 updatedt가 변경된 사용자 정보만이 반영됩니다.</t>
   </si>
 </sst>
 </file>
@@ -937,7 +940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:F35"/>
+  <dimension ref="B4:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -1307,6 +1310,11 @@
     <row r="35" spans="2:2">
       <c r="B35" s="8" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
